--- a/notebooks/AirportCoordinates.xlsx
+++ b/notebooks/AirportCoordinates.xlsx
@@ -40,9 +40,6 @@
     <t>Coimbatore International Airport, Avinashi Road, Peelamedu, Coimbatore, Tamil Nadu 641014</t>
   </si>
   <si>
-    <t>Coimbatore</t>
-  </si>
-  <si>
     <t>11.03003</t>
   </si>
   <si>
@@ -55,9 +52,6 @@
     <t>Birsa Munda Airport, Hinoo, Ranchi, Jharkhand 834002</t>
   </si>
   <si>
-    <t>Ranchi</t>
-  </si>
-  <si>
     <t>23.31425</t>
   </si>
   <si>
@@ -70,9 +64,6 @@
     <t>Goa International Airport, Airport Road, Dabolim, Goa 403801</t>
   </si>
   <si>
-    <t>Dabolim</t>
-  </si>
-  <si>
     <t>15.38083</t>
   </si>
   <si>
@@ -85,9 +76,6 @@
     <t>Sardar Vallabhbhai Patel International Airport, Hansol, Ahmedabad, Gujarat 380003</t>
   </si>
   <si>
-    <t>Ahmedabad</t>
-  </si>
-  <si>
     <t>23.07724</t>
   </si>
   <si>
@@ -100,9 +88,6 @@
     <t>Rajiv Gandhi International Airport, Shamshabad, Hyderabad, Telangana 500409</t>
   </si>
   <si>
-    <t>Hyderabad</t>
-  </si>
-  <si>
     <t>17.23132</t>
   </si>
   <si>
@@ -115,9 +100,6 @@
     <t>Agartala Airport, Agartala, Tripura 799009</t>
   </si>
   <si>
-    <t>Khowai</t>
-  </si>
-  <si>
     <t>23.88698</t>
   </si>
   <si>
@@ -145,18 +127,12 @@
     <t>Pune International Airport, Lohegaon, Pune, Maharashtra 411032</t>
   </si>
   <si>
-    <t>Pune</t>
-  </si>
-  <si>
     <t>Vijayawada Airport (VGA)</t>
   </si>
   <si>
     <t>Vijayawada Airport, Gannavaram, Andhra Pradesh 521102</t>
   </si>
   <si>
-    <t>Vijayawada</t>
-  </si>
-  <si>
     <t>16.53043</t>
   </si>
   <si>
@@ -169,9 +145,6 @@
     <t>Gwalior Airport, Maharajpur, Gwalior, Madhya Pradesh 474020</t>
   </si>
   <si>
-    <t>Gwalior</t>
-  </si>
-  <si>
     <t>26.29334</t>
   </si>
   <si>
@@ -184,9 +157,6 @@
     <t>Kempegowda International Airport, Devanahalli, Bengaluru, Karnataka 560300</t>
   </si>
   <si>
-    <t>Bengaluru</t>
-  </si>
-  <si>
     <t>13.20071</t>
   </si>
   <si>
@@ -199,9 +169,6 @@
     <t>Lokpriya Gopinath Bordoloi International Airport, Borjhar, Guwahati, Assam 781015</t>
   </si>
   <si>
-    <t>Guwahati</t>
-  </si>
-  <si>
     <t>26.10609</t>
   </si>
   <si>
@@ -214,9 +181,6 @@
     <t>Bilaspur Airport, Chakarbhata, Bilaspur, Chhattisgarh 495220</t>
   </si>
   <si>
-    <t>Bilaspur</t>
-  </si>
-  <si>
     <t>21.9884</t>
   </si>
   <si>
@@ -229,9 +193,6 @@
     <t>Swami Vivekananda Airport, Ramchandi, Naya Raipur, Chhattisgarh 492015</t>
   </si>
   <si>
-    <t>Raipur</t>
-  </si>
-  <si>
     <t>21.1804</t>
   </si>
   <si>
@@ -244,36 +205,24 @@
     <t>Puducherry Airport, Lawspet, Puducherry 605008</t>
   </si>
   <si>
-    <t>Puducherry</t>
-  </si>
-  <si>
     <t>Sonari Airport (IXW)</t>
   </si>
   <si>
     <t>Sonari Airport, Sonari, Jamshedpur, Jharkhand 831011</t>
   </si>
   <si>
-    <t>Jamshedpur</t>
-  </si>
-  <si>
     <t>Nashik International Airport (ISK)</t>
   </si>
   <si>
     <t>Nashik International Airport, Ozar, Nashik, Maharashtra 422221</t>
   </si>
   <si>
-    <t>Nashik</t>
-  </si>
-  <si>
     <t>Mopa International Airport (GOX)</t>
   </si>
   <si>
     <t>Mopa International Airport, Mopa, Pernem, Goa 403512</t>
   </si>
   <si>
-    <t>Mopa</t>
-  </si>
-  <si>
     <t>15.7313</t>
   </si>
   <si>
@@ -286,9 +235,6 @@
     <t>Prayagraj Airport, Bamrauli, Prayagraj, Uttar Pradesh 211012</t>
   </si>
   <si>
-    <t>Prayagraj</t>
-  </si>
-  <si>
     <t>25.44006</t>
   </si>
   <si>
@@ -301,9 +247,6 @@
     <t>Vadodara Airport, Harni Road, Vadodara, Gujarat 390022</t>
   </si>
   <si>
-    <t>Vadodara</t>
-  </si>
-  <si>
     <t>22.3362</t>
   </si>
   <si>
@@ -316,9 +259,6 @@
     <t>Ludhiana Airport, Sahnewal, Ludhiana, Punjab 141120</t>
   </si>
   <si>
-    <t>Ludhiana</t>
-  </si>
-  <si>
     <t>30.8547</t>
   </si>
   <si>
@@ -340,9 +280,6 @@
     <t>Chennai International Airport, GST Road, Meenambakkam, Chennai, Tamil Nadu 600027</t>
   </si>
   <si>
-    <t>Chennai</t>
-  </si>
-  <si>
     <t>12.98833</t>
   </si>
   <si>
@@ -355,9 +292,6 @@
     <t>Biju Patnaik International Airport, Airport Road, Bhubaneswar, Odisha 751020</t>
   </si>
   <si>
-    <t>Puri</t>
-  </si>
-  <si>
     <t>20.24436</t>
   </si>
   <si>
@@ -370,9 +304,6 @@
     <t>Tirupati Airport, Renigunta, Andhra Pradesh 517520</t>
   </si>
   <si>
-    <t>Tirupati</t>
-  </si>
-  <si>
     <t>13.6325</t>
   </si>
   <si>
@@ -385,9 +316,6 @@
     <t>Dehradun Airport, Jolly Grant, Dehradun, Uttarakhand 248140</t>
   </si>
   <si>
-    <t>Dehradun</t>
-  </si>
-  <si>
     <t>30.1897</t>
   </si>
   <si>
@@ -400,9 +328,6 @@
     <t>Sheikh ul-Alam International Airport, Aerodrome Road, Srinagar, Jammu and Kashmir 190007</t>
   </si>
   <si>
-    <t>Srinagar</t>
-  </si>
-  <si>
     <t>33.9871</t>
   </si>
   <si>
@@ -415,9 +340,6 @@
     <t>Indira Gandhi International Airport, New Delhi, Delhi 110037</t>
   </si>
   <si>
-    <t>Delhi NCR</t>
-  </si>
-  <si>
     <t>28.5665</t>
   </si>
   <si>
@@ -430,27 +352,18 @@
     <t>Donyi Polo Airport, Hollongi, Itanagar, Arunachal Pradesh 791123</t>
   </si>
   <si>
-    <t>Itanagar</t>
-  </si>
-  <si>
     <t>Lal Bahadur Shastri International Airport (VNS)</t>
   </si>
   <si>
     <t>Lal Bahadur Shastri International Airport, Babatpur, Varanasi, Uttar Pradesh 221006</t>
   </si>
   <si>
-    <t>Varanasi</t>
-  </si>
-  <si>
     <t>Rupsi Airport (RUP)</t>
   </si>
   <si>
     <t>Rupsi Airport, Rupsi, Assam 783372</t>
   </si>
   <si>
-    <t>Dhubri</t>
-  </si>
-  <si>
     <t>26.14118</t>
   </si>
   <si>
@@ -463,9 +376,6 @@
     <t>Netaji Subhas Chandra Bose International Airport, Jessore Road, Dum Dum, Kolkata, West Bengal 700052</t>
   </si>
   <si>
-    <t>Kolkata</t>
-  </si>
-  <si>
     <t>22.65474</t>
   </si>
   <si>
@@ -478,9 +388,6 @@
     <t>Pakyong Airport, Pakyong, Sikkim 737106</t>
   </si>
   <si>
-    <t>Gangtok</t>
-  </si>
-  <si>
     <t>27.22756</t>
   </si>
   <si>
@@ -493,9 +400,6 @@
     <t>Shillong Airport, Umroi, Meghalaya 793103</t>
   </si>
   <si>
-    <t>Shillong</t>
-  </si>
-  <si>
     <t>25.7036</t>
   </si>
   <si>
@@ -508,9 +412,6 @@
     <t>Sri Guru Ram Dass Jee International Airport, Ajnala Road, Amritsar, Punjab 143101</t>
   </si>
   <si>
-    <t>Amritsar</t>
-  </si>
-  <si>
     <t>31.70959</t>
   </si>
   <si>
@@ -523,9 +424,6 @@
     <t>Raja Bhoj Airport, Gandhi Nagar, Bhopal, Madhya Pradesh 462036</t>
   </si>
   <si>
-    <t>Bhopal</t>
-  </si>
-  <si>
     <t>23.28747</t>
   </si>
   <si>
@@ -538,9 +436,6 @@
     <t>Jaipur International Airport, Airport Road, Sanganer, Jaipur, Rajasthan 302029</t>
   </si>
   <si>
-    <t>Jaipur</t>
-  </si>
-  <si>
     <t>26.82419</t>
   </si>
   <si>
@@ -553,9 +448,6 @@
     <t>Kullu–Manali Airport, Bhuntar, Kullu, Himachal Pradesh 175125</t>
   </si>
   <si>
-    <t>Kullu-Manali</t>
-  </si>
-  <si>
     <t>Ayodhya Airport (under construction)</t>
   </si>
   <si>
@@ -565,18 +457,12 @@
     <t>Ayodhya</t>
   </si>
   <si>
-    <t>Bhubaneswar</t>
-  </si>
-  <si>
     <t>Trivandrum International Airport (TRV)</t>
   </si>
   <si>
     <t>Trivandrum International Airport, Vallakkadavu, Thiruvananthapuram, Kerala 695008</t>
   </si>
   <si>
-    <t>Thiruvananthapuram</t>
-  </si>
-  <si>
     <t>8.48212</t>
   </si>
   <si>
@@ -589,9 +475,6 @@
     <t>Kota Airport, Aerodrome Circle, Kota, Rajasthan 324007</t>
   </si>
   <si>
-    <t>Kota</t>
-  </si>
-  <si>
     <t>25.16022</t>
   </si>
   <si>
@@ -604,9 +487,6 @@
     <t>Surat Airport, Dumas Road, Surat, Gujarat 395007</t>
   </si>
   <si>
-    <t>Surat</t>
-  </si>
-  <si>
     <t>21.1141</t>
   </si>
   <si>
@@ -619,9 +499,6 @@
     <t>Maharana Pratap Airport, NH 76, Dabok, Udaipur, Rajasthan 313022</t>
   </si>
   <si>
-    <t>Udaipur</t>
-  </si>
-  <si>
     <t>24.61784</t>
   </si>
   <si>
@@ -634,9 +511,6 @@
     <t>Diu Airport, Diu, Daman and Diu 362520</t>
   </si>
   <si>
-    <t>Diu</t>
-  </si>
-  <si>
     <t>20.7131</t>
   </si>
   <si>
@@ -649,9 +523,6 @@
     <t>Chandigarh International Airport, Mohali, Punjab 160004</t>
   </si>
   <si>
-    <t>Chandigarh</t>
-  </si>
-  <si>
     <t>30.6735</t>
   </si>
   <si>
@@ -664,9 +535,6 @@
     <t>Shimla Airport, Jubbarhatti, Shimla, Himachal Pradesh 171011</t>
   </si>
   <si>
-    <t>Shimla</t>
-  </si>
-  <si>
     <t>31.0818</t>
   </si>
   <si>
@@ -679,9 +547,6 @@
     <t>Imphal International Airport, Imphal, Manipur 795140</t>
   </si>
   <si>
-    <t>Imphal</t>
-  </si>
-  <si>
     <t>24.75995</t>
   </si>
   <si>
@@ -694,9 +559,6 @@
     <t>Hisar Airport, Hisar, Haryana 125001</t>
   </si>
   <si>
-    <t>Hisar</t>
-  </si>
-  <si>
     <t>29.17944</t>
   </si>
   <si>
@@ -709,9 +571,6 @@
     <t>Visakhapatnam Airport, NAD Junction, Visakhapatnam, Andhra Pradesh 530009</t>
   </si>
   <si>
-    <t>Visakhapatnam</t>
-  </si>
-  <si>
     <t>17.7212</t>
   </si>
   <si>
@@ -724,18 +583,12 @@
     <t>Devi Ahilya Bai Holkar Airport, Indore, Madhya Pradesh 452005</t>
   </si>
   <si>
-    <t>Indore</t>
-  </si>
-  <si>
     <t>Mysore Airport (MYQ)</t>
   </si>
   <si>
     <t>Mysore Airport, Mandakalli, Mysuru, Karnataka 570008</t>
   </si>
   <si>
-    <t>Mysuru</t>
-  </si>
-  <si>
     <t>12.3072</t>
   </si>
   <si>
@@ -748,16 +601,163 @@
     <t>Jay Prakash Narayan Airport, Sheikhpura, Patna, Bihar 800014</t>
   </si>
   <si>
-    <t>Patna</t>
-  </si>
-  <si>
-    <t>Mumbai</t>
-  </si>
-  <si>
     <t>Biju Patnaik International Airport (BAI)</t>
   </si>
   <si>
     <t>Chhatrapati Shivaji Maharaj International Airport (BOmm)</t>
+  </si>
+  <si>
+    <t>Coimbatore (CJB)</t>
+  </si>
+  <si>
+    <t>Ranchi (IXR)</t>
+  </si>
+  <si>
+    <t>Dabolim (GOI)</t>
+  </si>
+  <si>
+    <t>Ahmedabad (AMD)</t>
+  </si>
+  <si>
+    <t>Hyderabad (HYD)</t>
+  </si>
+  <si>
+    <t>Khowai (IXA)</t>
+  </si>
+  <si>
+    <t>Pune (PNQ)</t>
+  </si>
+  <si>
+    <t>Vijayawada (VGA)</t>
+  </si>
+  <si>
+    <t>Gwalior (GWL)</t>
+  </si>
+  <si>
+    <t>Bengaluru (BLR)</t>
+  </si>
+  <si>
+    <t>Guwahati (GAU)</t>
+  </si>
+  <si>
+    <t>Bilaspur (PAB)</t>
+  </si>
+  <si>
+    <t>Raipur (RPR)</t>
+  </si>
+  <si>
+    <t>Puducherry (PNY)</t>
+  </si>
+  <si>
+    <t>Jamshedpur (IXW)</t>
+  </si>
+  <si>
+    <t>Nashik (ISK)</t>
+  </si>
+  <si>
+    <t>Mopa (GOX)</t>
+  </si>
+  <si>
+    <t>Prayagraj (IXD)</t>
+  </si>
+  <si>
+    <t>Vadodara (BDQ)</t>
+  </si>
+  <si>
+    <t>Ludhiana (LUH)</t>
+  </si>
+  <si>
+    <t>Chennai (MAA)</t>
+  </si>
+  <si>
+    <t>Puri (BAI)</t>
+  </si>
+  <si>
+    <t>Tirupati (TIR)</t>
+  </si>
+  <si>
+    <t>Dehradun (DED)</t>
+  </si>
+  <si>
+    <t>Srinagar (SXR)</t>
+  </si>
+  <si>
+    <t>Delhi NCR (DEL)</t>
+  </si>
+  <si>
+    <t>Itanagar (HGI)</t>
+  </si>
+  <si>
+    <t>Varanasi (VNS)</t>
+  </si>
+  <si>
+    <t>Dhubri (RUP)</t>
+  </si>
+  <si>
+    <t>Kolkata (CCU)</t>
+  </si>
+  <si>
+    <t>Gangtok (PYG)</t>
+  </si>
+  <si>
+    <t>Shillong (SHL)</t>
+  </si>
+  <si>
+    <t>Amritsar (ATQ)</t>
+  </si>
+  <si>
+    <t>Bhopal (BHO)</t>
+  </si>
+  <si>
+    <t>Jaipur (JAI)</t>
+  </si>
+  <si>
+    <t>Kullu-Manali (KUU)</t>
+  </si>
+  <si>
+    <t>Bhubaneswar (BBI)</t>
+  </si>
+  <si>
+    <t>Thiruvananthapuram (TRV)</t>
+  </si>
+  <si>
+    <t>Kota (KTU)</t>
+  </si>
+  <si>
+    <t>Surat (STV)</t>
+  </si>
+  <si>
+    <t>Udaipur (UDR)</t>
+  </si>
+  <si>
+    <t>Diu (DIU)</t>
+  </si>
+  <si>
+    <t>Chandigarh (IXC)</t>
+  </si>
+  <si>
+    <t>Shimla (SLV)</t>
+  </si>
+  <si>
+    <t>Imphal (IMF)</t>
+  </si>
+  <si>
+    <t>Hisar (HSS)</t>
+  </si>
+  <si>
+    <t>Visakhapatnam (VTZ)</t>
+  </si>
+  <si>
+    <t>Indore (IDR)</t>
+  </si>
+  <si>
+    <t>Mysuru (MYQ)</t>
+  </si>
+  <si>
+    <t>Patna (PAT)</t>
+  </si>
+  <si>
+    <t>Mumbai (BOM)</t>
   </si>
 </sst>
 </file>
@@ -1121,11 +1121,10 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="51.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="95.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1159,13 +1158,13 @@
         <v>7</v>
       </c>
       <c r="D2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1173,19 +1172,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1193,19 +1192,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>199</v>
+      </c>
+      <c r="E4" t="s">
         <v>16</v>
       </c>
-      <c r="C4" t="s">
+      <c r="F4" t="s">
         <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1213,19 +1212,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>200</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" t="s">
         <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1233,19 +1232,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>201</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1253,19 +1252,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>202</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1273,19 +1272,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>247</v>
+        <v>196</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1293,13 +1292,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>203</v>
       </c>
       <c r="E9">
         <v>18.34</v>
@@ -1313,19 +1312,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>204</v>
       </c>
       <c r="E10" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F10" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1333,19 +1332,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>205</v>
       </c>
       <c r="E11" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1353,19 +1352,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>206</v>
       </c>
       <c r="E12" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1373,19 +1372,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>61</v>
+        <v>207</v>
       </c>
       <c r="E13" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1393,19 +1392,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C14" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="D14" t="s">
-        <v>66</v>
+        <v>208</v>
       </c>
       <c r="E14" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="F14" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1413,19 +1412,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="D15" t="s">
-        <v>71</v>
+        <v>209</v>
       </c>
       <c r="E15" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="F15" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1433,13 +1432,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="C16" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="D16" t="s">
-        <v>76</v>
+        <v>210</v>
       </c>
       <c r="E16">
         <v>11.58</v>
@@ -1453,13 +1452,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="D17" t="s">
-        <v>79</v>
+        <v>211</v>
       </c>
       <c r="E17">
         <v>22.48</v>
@@ -1473,13 +1472,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C18" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="D18" t="s">
-        <v>82</v>
+        <v>212</v>
       </c>
       <c r="E18">
         <v>20.119444000000001</v>
@@ -1493,19 +1492,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="D19" t="s">
-        <v>85</v>
+        <v>213</v>
       </c>
       <c r="E19" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="F19" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1513,19 +1512,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="C20" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="D20" t="s">
-        <v>90</v>
+        <v>214</v>
       </c>
       <c r="E20" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="F20" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1533,19 +1532,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="D21" t="s">
-        <v>95</v>
+        <v>215</v>
       </c>
       <c r="E21" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="F21" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1553,19 +1552,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="C22" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="D22" t="s">
-        <v>100</v>
+        <v>216</v>
       </c>
       <c r="E22" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="F22" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1573,13 +1572,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="D23" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="E23">
         <v>21.823889000000001</v>
@@ -1593,19 +1592,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="D24" t="s">
-        <v>108</v>
+        <v>217</v>
       </c>
       <c r="E24" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="F24" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1613,19 +1612,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>246</v>
+        <v>195</v>
       </c>
       <c r="C25" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="D25" t="s">
-        <v>113</v>
+        <v>218</v>
       </c>
       <c r="E25" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="F25" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1633,19 +1632,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="C26" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="D26" t="s">
-        <v>118</v>
+        <v>219</v>
       </c>
       <c r="E26" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="F26" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1653,19 +1652,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="C27" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="D27" t="s">
-        <v>123</v>
+        <v>220</v>
       </c>
       <c r="E27" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="F27" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1673,19 +1672,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="C28" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="D28" t="s">
-        <v>128</v>
+        <v>221</v>
       </c>
       <c r="E28" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="F28" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1693,19 +1692,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="C29" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="D29" t="s">
-        <v>133</v>
+        <v>222</v>
       </c>
       <c r="E29" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="F29" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1713,13 +1712,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="C30" t="s">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="D30" t="s">
-        <v>138</v>
+        <v>223</v>
       </c>
       <c r="E30">
         <v>26.97</v>
@@ -1733,13 +1732,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="C31" t="s">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="D31" t="s">
-        <v>141</v>
+        <v>224</v>
       </c>
       <c r="E31">
         <v>25.452221999999999</v>
@@ -1753,19 +1752,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="C32" t="s">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="D32" t="s">
-        <v>144</v>
+        <v>225</v>
       </c>
       <c r="E32" t="s">
-        <v>145</v>
+        <v>116</v>
       </c>
       <c r="F32" t="s">
-        <v>146</v>
+        <v>117</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1773,19 +1772,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>147</v>
+        <v>118</v>
       </c>
       <c r="C33" t="s">
-        <v>148</v>
+        <v>119</v>
       </c>
       <c r="D33" t="s">
-        <v>149</v>
+        <v>226</v>
       </c>
       <c r="E33" t="s">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="F33" t="s">
-        <v>151</v>
+        <v>121</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1793,19 +1792,19 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="C34" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="D34" t="s">
-        <v>154</v>
+        <v>227</v>
       </c>
       <c r="E34" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="F34" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -1813,19 +1812,19 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="C35" t="s">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="D35" t="s">
-        <v>159</v>
+        <v>228</v>
       </c>
       <c r="E35" t="s">
-        <v>160</v>
+        <v>128</v>
       </c>
       <c r="F35" t="s">
-        <v>161</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -1833,19 +1832,19 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>162</v>
+        <v>130</v>
       </c>
       <c r="C36" t="s">
-        <v>163</v>
+        <v>131</v>
       </c>
       <c r="D36" t="s">
-        <v>164</v>
+        <v>229</v>
       </c>
       <c r="E36" t="s">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="F36" t="s">
-        <v>166</v>
+        <v>133</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -1853,19 +1852,19 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>167</v>
+        <v>134</v>
       </c>
       <c r="C37" t="s">
-        <v>168</v>
+        <v>135</v>
       </c>
       <c r="D37" t="s">
-        <v>169</v>
+        <v>230</v>
       </c>
       <c r="E37" t="s">
-        <v>170</v>
+        <v>136</v>
       </c>
       <c r="F37" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1873,19 +1872,19 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>172</v>
+        <v>138</v>
       </c>
       <c r="C38" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="D38" t="s">
-        <v>174</v>
+        <v>231</v>
       </c>
       <c r="E38" t="s">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="F38" t="s">
-        <v>176</v>
+        <v>141</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1893,13 +1892,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>177</v>
+        <v>142</v>
       </c>
       <c r="C39" t="s">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="D39" t="s">
-        <v>179</v>
+        <v>232</v>
       </c>
       <c r="E39">
         <v>31.876667000000001</v>
@@ -1913,13 +1912,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>180</v>
+        <v>144</v>
       </c>
       <c r="C40" t="s">
-        <v>181</v>
+        <v>145</v>
       </c>
       <c r="D40" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="E40">
         <v>26.748034000000001</v>
@@ -1933,19 +1932,19 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="C41" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="D41" t="s">
-        <v>183</v>
+        <v>233</v>
       </c>
       <c r="E41" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="F41" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -1953,19 +1952,19 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>184</v>
+        <v>147</v>
       </c>
       <c r="C42" t="s">
-        <v>185</v>
+        <v>148</v>
       </c>
       <c r="D42" t="s">
-        <v>186</v>
+        <v>234</v>
       </c>
       <c r="E42" t="s">
-        <v>187</v>
+        <v>149</v>
       </c>
       <c r="F42" t="s">
-        <v>188</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -1973,19 +1972,19 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>189</v>
+        <v>151</v>
       </c>
       <c r="C43" t="s">
-        <v>190</v>
+        <v>152</v>
       </c>
       <c r="D43" t="s">
-        <v>191</v>
+        <v>235</v>
       </c>
       <c r="E43" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="F43" t="s">
-        <v>193</v>
+        <v>154</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -1993,19 +1992,19 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>194</v>
+        <v>155</v>
       </c>
       <c r="C44" t="s">
-        <v>195</v>
+        <v>156</v>
       </c>
       <c r="D44" t="s">
-        <v>196</v>
+        <v>236</v>
       </c>
       <c r="E44" t="s">
-        <v>197</v>
+        <v>157</v>
       </c>
       <c r="F44" t="s">
-        <v>198</v>
+        <v>158</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -2013,19 +2012,19 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>199</v>
+        <v>159</v>
       </c>
       <c r="C45" t="s">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="D45" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="E45" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="F45" t="s">
-        <v>203</v>
+        <v>162</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -2033,19 +2032,19 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>204</v>
+        <v>163</v>
       </c>
       <c r="C46" t="s">
-        <v>205</v>
+        <v>164</v>
       </c>
       <c r="D46" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="E46" t="s">
-        <v>207</v>
+        <v>165</v>
       </c>
       <c r="F46" t="s">
-        <v>208</v>
+        <v>166</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -2053,19 +2052,19 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>209</v>
+        <v>167</v>
       </c>
       <c r="C47" t="s">
-        <v>210</v>
+        <v>168</v>
       </c>
       <c r="D47" t="s">
-        <v>211</v>
+        <v>239</v>
       </c>
       <c r="E47" t="s">
-        <v>212</v>
+        <v>169</v>
       </c>
       <c r="F47" t="s">
-        <v>213</v>
+        <v>170</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -2073,19 +2072,19 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>214</v>
+        <v>171</v>
       </c>
       <c r="C48" t="s">
-        <v>215</v>
+        <v>172</v>
       </c>
       <c r="D48" t="s">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="E48" t="s">
-        <v>217</v>
+        <v>173</v>
       </c>
       <c r="F48" t="s">
-        <v>218</v>
+        <v>174</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -2093,19 +2092,19 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>219</v>
+        <v>175</v>
       </c>
       <c r="C49" t="s">
-        <v>220</v>
+        <v>176</v>
       </c>
       <c r="D49" t="s">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="E49" t="s">
-        <v>222</v>
+        <v>177</v>
       </c>
       <c r="F49" t="s">
-        <v>223</v>
+        <v>178</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -2113,19 +2112,19 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>224</v>
+        <v>179</v>
       </c>
       <c r="C50" t="s">
-        <v>225</v>
+        <v>180</v>
       </c>
       <c r="D50" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="E50" t="s">
-        <v>227</v>
+        <v>181</v>
       </c>
       <c r="F50" t="s">
-        <v>228</v>
+        <v>182</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -2133,19 +2132,19 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>229</v>
+        <v>183</v>
       </c>
       <c r="C51" t="s">
-        <v>230</v>
+        <v>184</v>
       </c>
       <c r="D51" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="E51" t="s">
-        <v>232</v>
+        <v>185</v>
       </c>
       <c r="F51" t="s">
-        <v>233</v>
+        <v>186</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -2153,13 +2152,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>234</v>
+        <v>187</v>
       </c>
       <c r="C52" t="s">
-        <v>235</v>
+        <v>188</v>
       </c>
       <c r="D52" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="E52">
         <v>22.721667</v>
@@ -2173,19 +2172,19 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>237</v>
+        <v>189</v>
       </c>
       <c r="C53" t="s">
-        <v>238</v>
+        <v>190</v>
       </c>
       <c r="D53" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="E53" t="s">
-        <v>240</v>
+        <v>191</v>
       </c>
       <c r="F53" t="s">
-        <v>241</v>
+        <v>192</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -2193,13 +2192,13 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>242</v>
+        <v>193</v>
       </c>
       <c r="C54" t="s">
-        <v>243</v>
+        <v>194</v>
       </c>
       <c r="D54" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E54">
         <v>25.591388999999999</v>
@@ -2213,22 +2212,23 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C55" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D55" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E55" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F55" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>